--- a/test/exp2.xlsx
+++ b/test/exp2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abhiraj Das\Documents\DMSBackend\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{659B462A-E4AD-4019-87B0-C049BAF246AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0236025-7288-4FF9-AA43-A6BAD122AAE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -130,27 +130,12 @@
     <t>9876543210</t>
   </si>
   <si>
-    <t>INV001</t>
-  </si>
-  <si>
-    <t>John Doe</t>
-  </si>
-  <si>
-    <t>PAN1234567</t>
-  </si>
-  <si>
     <t>john@example.com</t>
   </si>
   <si>
     <t>Dell Inspiron</t>
   </si>
   <si>
-    <t>8471</t>
-  </si>
-  <si>
-    <t>50000</t>
-  </si>
-  <si>
     <t>B2B</t>
   </si>
   <si>
@@ -163,9 +148,6 @@
     <t>8472</t>
   </si>
   <si>
-    <t>1500</t>
-  </si>
-  <si>
     <t>mumbai</t>
   </si>
   <si>
@@ -190,23 +172,41 @@
     <t>ddddddd</t>
   </si>
   <si>
-    <t>GST001313131</t>
-  </si>
-  <si>
-    <t>MALAD WEST</t>
-  </si>
-  <si>
-    <t>Board</t>
-  </si>
-  <si>
     <t>RIDER HELMET</t>
+  </si>
+  <si>
+    <t>ASDFG7410L</t>
+  </si>
+  <si>
+    <t>Malad east</t>
+  </si>
+  <si>
+    <t>INV002</t>
+  </si>
+  <si>
+    <t>GST001313132</t>
+  </si>
+  <si>
+    <t>Renuka</t>
+  </si>
+  <si>
+    <t>Book</t>
+  </si>
+  <si>
+    <t>8473</t>
+  </si>
+  <si>
+    <t>50001</t>
+  </si>
+  <si>
+    <t>1501</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -218,6 +218,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -568,7 +574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AJ8"/>
+  <dimension ref="A1:AJ7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
@@ -623,7 +629,7 @@
         <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>15</v>
@@ -688,52 +694,52 @@
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2">
+        <v>7894561231</v>
+      </c>
+      <c r="D2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" t="s">
         <v>48</v>
       </c>
-      <c r="B2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C2">
-        <v>11111111111</v>
-      </c>
-      <c r="D2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" s="2">
+        <v>43953</v>
+      </c>
+      <c r="I2" t="s">
         <v>53</v>
       </c>
-      <c r="F2" t="s">
+      <c r="J2" s="2">
+        <v>37378</v>
+      </c>
+      <c r="K2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M2" t="s">
+        <v>55</v>
+      </c>
+      <c r="N2" t="s">
         <v>54</v>
       </c>
-      <c r="G2" t="s">
-        <v>55</v>
-      </c>
-      <c r="H2" s="2">
-        <v>43961</v>
-      </c>
-      <c r="I2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J2" s="2">
-        <v>37387</v>
-      </c>
-      <c r="K2" t="s">
-        <v>49</v>
-      </c>
-      <c r="L2" t="s">
-        <v>49</v>
-      </c>
-      <c r="M2" t="s">
-        <v>37</v>
-      </c>
-      <c r="N2" t="s">
-        <v>56</v>
-      </c>
       <c r="O2" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="P2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="Q2">
         <v>1</v>
@@ -745,16 +751,16 @@
         <v>0</v>
       </c>
       <c r="T2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="U2" t="s">
         <v>35</v>
       </c>
       <c r="V2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="W2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="X2" t="s">
         <v>41</v>
@@ -763,34 +769,34 @@
         <v>1200</v>
       </c>
       <c r="Z2" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="AA2">
         <v>18</v>
       </c>
       <c r="AB2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="AC2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="AD2">
         <v>6</v>
       </c>
       <c r="AE2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="AF2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="AG2" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="AH2">
         <v>1500</v>
       </c>
       <c r="AI2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="AJ2">
         <v>18</v>
@@ -816,11 +822,8 @@
       <c r="H7" s="2"/>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="H8" s="2"/>
-      <c r="J8" s="2"/>
-    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>